--- a/data/trans_orig/P19C03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C03-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126944</t>
+          <t>125603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>171044</t>
+          <t>169626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191758</t>
+          <t>193488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>245324</t>
+          <t>245701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>332507</t>
+          <t>332736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>401227</t>
+          <t>398954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>517281</t>
+          <t>518699</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>561381</t>
+          <t>562722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>713635</t>
+          <t>713258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>767201</t>
+          <t>765471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1246057</t>
+          <t>1248330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1314777</t>
+          <t>1314548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>457407</t>
+          <t>460849</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>531189</t>
+          <t>531679</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>498746</t>
+          <t>492907</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>568307</t>
+          <t>568958</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>977621</t>
+          <t>977389</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1075721</t>
+          <t>1078371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>783259</t>
+          <t>782769</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>857041</t>
+          <t>853599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>804888</t>
+          <t>804237</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>874449</t>
+          <t>880288</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1611922</t>
+          <t>1609272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1710022</t>
+          <t>1710254</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125246</t>
+          <t>122506</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164205</t>
+          <t>163090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111916</t>
+          <t>109718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150261</t>
+          <t>147397</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>245507</t>
+          <t>243975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>302551</t>
+          <t>300164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>286724</t>
+          <t>287839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325683</t>
+          <t>328423</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258522</t>
+          <t>261386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>296867</t>
+          <t>299065</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>557161</t>
+          <t>559548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>614205</t>
+          <t>615737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>738000</t>
+          <t>738252</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>835283</t>
+          <t>831122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>825485</t>
+          <t>832173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>928483</t>
+          <t>926843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1595910</t>
+          <t>1600758</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1728616</t>
+          <t>1731109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1618418</t>
+          <t>1622579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1715701</t>
+          <t>1715449</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1812454</t>
+          <t>1814094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1915452</t>
+          <t>1908764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3466022</t>
+          <t>3463529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3598728</t>
+          <t>3593880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129076</t>
+          <t>129084</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173246</t>
+          <t>174337</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>241465</t>
+          <t>238453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>299045</t>
+          <t>297879</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>383989</t>
+          <t>385045</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>455471</t>
+          <t>461486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>604975</t>
+          <t>603884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>649145</t>
+          <t>649137</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>829282</t>
+          <t>830448</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>886862</t>
+          <t>889874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1451076</t>
+          <t>1445061</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1522558</t>
+          <t>1521502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>545422</t>
+          <t>540199</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>625489</t>
+          <t>623988</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>494887</t>
+          <t>497157</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>569760</t>
+          <t>576779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1061305</t>
+          <t>1061373</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1169035</t>
+          <t>1172656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1060955</t>
+          <t>1062456</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1141022</t>
+          <t>1146245</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1020518</t>
+          <t>1013499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1095391</t>
+          <t>1093121</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2107686</t>
+          <t>2104065</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2215416</t>
+          <t>2215348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121853</t>
+          <t>122420</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>165134</t>
+          <t>162598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93595</t>
+          <t>91778</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130538</t>
+          <t>131144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>227364</t>
+          <t>224530</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>283029</t>
+          <t>282327</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277000</t>
+          <t>279536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320281</t>
+          <t>319714</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>291262</t>
+          <t>290656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328205</t>
+          <t>330022</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>580905</t>
+          <t>581607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>636570</t>
+          <t>639404</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>74,01%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>823753</t>
+          <t>826881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>924825</t>
+          <t>927212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>861144</t>
+          <t>857377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>964626</t>
+          <t>964574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1713472</t>
+          <t>1711695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1861730</t>
+          <t>1860171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1981973</t>
+          <t>1979586</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2083045</t>
+          <t>2079917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2175779</t>
+          <t>2175831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2279261</t>
+          <t>2283028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4185473</t>
+          <t>4187032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4333731</t>
+          <t>4335508</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,69%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75363</t>
+          <t>76402</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108562</t>
+          <t>110573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119787</t>
+          <t>123691</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>163792</t>
+          <t>163644</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209407</t>
+          <t>207077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>266180</t>
+          <t>258808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>348857</t>
+          <t>346846</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>382056</t>
+          <t>381017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>475082</t>
+          <t>475230</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>519087</t>
+          <t>515183</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>830113</t>
+          <t>837485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>886886</t>
+          <t>889216</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>478885</t>
+          <t>475979</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>552452</t>
+          <t>554586</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>459722</t>
+          <t>457239</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>536603</t>
+          <t>531074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>955569</t>
+          <t>951845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1070139</t>
+          <t>1062309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1144153</t>
+          <t>1142019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1217720</t>
+          <t>1220626</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1172116</t>
+          <t>1177645</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1248997</t>
+          <t>1251480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2335185</t>
+          <t>2343015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2449755</t>
+          <t>2453479</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105618</t>
+          <t>105268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148223</t>
+          <t>145355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93023</t>
+          <t>93524</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129195</t>
+          <t>130325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>209240</t>
+          <t>213592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>266876</t>
+          <t>267601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>351021</t>
+          <t>353889</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>393626</t>
+          <t>393976</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>379125</t>
+          <t>377995</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>415297</t>
+          <t>414796</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>740688</t>
+          <t>739963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>798324</t>
+          <t>793972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>684457</t>
+          <t>687976</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>776562</t>
+          <t>783656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>697129</t>
+          <t>700814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>792775</t>
+          <t>791991</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1413050</t>
+          <t>1413411</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1544474</t>
+          <t>1549998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1876707</t>
+          <t>1869613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1968812</t>
+          <t>1965293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2063138</t>
+          <t>2063922</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2158784</t>
+          <t>2155099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3964708</t>
+          <t>3959184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4096132</t>
+          <t>4095771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2023 (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57629</t>
+          <t>57664</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87397</t>
+          <t>86944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90198</t>
+          <t>91433</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122150</t>
+          <t>121682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>157248</t>
+          <t>154606</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>200022</t>
+          <t>199094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395948</t>
+          <t>396401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425716</t>
+          <t>425681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>599466</t>
+          <t>599934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>631418</t>
+          <t>630183</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1004939</t>
+          <t>1005867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1047713</t>
+          <t>1050355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>282457</t>
+          <t>295770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>491711</t>
+          <t>495897</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>293891</t>
+          <t>297009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>483672</t>
+          <t>478431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>655542</t>
+          <t>670396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>943621</t>
+          <t>945230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1738826</t>
+          <t>1734640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1948080</t>
+          <t>1934767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1713591</t>
+          <t>1718832</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1903372</t>
+          <t>1900254</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3484178</t>
+          <t>3482569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3772257</t>
+          <t>3757403</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86514</t>
+          <t>86986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127618</t>
+          <t>128196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103978</t>
+          <t>104154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137724</t>
+          <t>136708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>198807</t>
+          <t>200391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>253754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503698</t>
+          <t>503120</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544802</t>
+          <t>544330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>513887</t>
+          <t>514903</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>547633</t>
+          <t>547457</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1029928</t>
+          <t>1029173</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1084120</t>
+          <t>1082536</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,38%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>456793</t>
+          <t>458468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>677103</t>
+          <t>675248</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>510788</t>
+          <t>528827</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>715269</t>
+          <t>714965</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1069274</t>
+          <t>1062306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1341860</t>
+          <t>1347249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2668094</t>
+          <t>2669949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2888404</t>
+          <t>2886729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2855221</t>
+          <t>2855525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3059702</t>
+          <t>3041663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5573827</t>
+          <t>5568438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5846413</t>
+          <t>5853381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C03-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>125603</t>
+          <t>125668</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169626</t>
+          <t>168534</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>193488</t>
+          <t>194924</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>245701</t>
+          <t>245564</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>332736</t>
+          <t>332537</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>398954</t>
+          <t>397955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>518699</t>
+          <t>519791</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>562722</t>
+          <t>562657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>713258</t>
+          <t>713395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>765471</t>
+          <t>764035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1248330</t>
+          <t>1249329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1314548</t>
+          <t>1314747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>460849</t>
+          <t>460285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>531679</t>
+          <t>528399</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>492907</t>
+          <t>497057</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>568958</t>
+          <t>567908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>977389</t>
+          <t>975683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1078371</t>
+          <t>1073008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>782769</t>
+          <t>786049</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>853599</t>
+          <t>854163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>804237</t>
+          <t>805287</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>880288</t>
+          <t>876138</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1609272</t>
+          <t>1614635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1710254</t>
+          <t>1711960</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,7%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122506</t>
+          <t>121973</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163090</t>
+          <t>164563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,47 +1434,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>27,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>36,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>128530</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>111085</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>149174</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>27,17%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>128530</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>109718</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>147397</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>26,84%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243975</t>
+          <t>245937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>300164</t>
+          <t>301506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>287839</t>
+          <t>286366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>328423</t>
+          <t>328956</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,49 +1547,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>72,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>280253</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>259609</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>297698</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>68,56%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>63,51%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>72,83%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>280253</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>261386</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>299065</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>68,56%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>63,94%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>73,16%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>556</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>559548</t>
+          <t>558206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>615737</t>
+          <t>613775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>738252</t>
+          <t>736551</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>831122</t>
+          <t>833872</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>832173</t>
+          <t>826844</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>926843</t>
+          <t>928824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1600758</t>
+          <t>1590088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1731109</t>
+          <t>1727432</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1622579</t>
+          <t>1619829</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1715449</t>
+          <t>1717150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1814094</t>
+          <t>1812113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1908764</t>
+          <t>1914093</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3463529</t>
+          <t>3467206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3593880</t>
+          <t>3604550</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129084</t>
+          <t>130689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174337</t>
+          <t>174607</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>238453</t>
+          <t>240651</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>297879</t>
+          <t>297482</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>385045</t>
+          <t>376866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>461486</t>
+          <t>455072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>603884</t>
+          <t>603614</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>649137</t>
+          <t>647532</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>830448</t>
+          <t>830845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>889874</t>
+          <t>887676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1445061</t>
+          <t>1451475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1521502</t>
+          <t>1529681</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>540199</t>
+          <t>539218</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>623988</t>
+          <t>619716</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>497157</t>
+          <t>493768</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>576779</t>
+          <t>571975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1061373</t>
+          <t>1057308</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1172656</t>
+          <t>1167344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1062456</t>
+          <t>1066728</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1146245</t>
+          <t>1147226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1013499</t>
+          <t>1018303</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1093121</t>
+          <t>1096510</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2104065</t>
+          <t>2109377</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2215348</t>
+          <t>2219413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122420</t>
+          <t>120848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162598</t>
+          <t>162374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91778</t>
+          <t>91209</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131144</t>
+          <t>130086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224530</t>
+          <t>225267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>282327</t>
+          <t>281675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279536</t>
+          <t>279760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>319714</t>
+          <t>321286</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>290656</t>
+          <t>291714</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330022</t>
+          <t>330591</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>581607</t>
+          <t>582259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639404</t>
+          <t>638667</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>826881</t>
+          <t>825074</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>927212</t>
+          <t>927386</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>857377</t>
+          <t>867097</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>964574</t>
+          <t>968905</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1711695</t>
+          <t>1716379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1860171</t>
+          <t>1860138</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1979586</t>
+          <t>1979412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2079917</t>
+          <t>2081724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2175831</t>
+          <t>2171500</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2283028</t>
+          <t>2273308</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4187032</t>
+          <t>4187065</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4335508</t>
+          <t>4330824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76402</t>
+          <t>74123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110573</t>
+          <t>108930</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123691</t>
+          <t>121329</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>163644</t>
+          <t>163984</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207077</t>
+          <t>206479</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258808</t>
+          <t>259738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>346846</t>
+          <t>348489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>381017</t>
+          <t>383296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>475230</t>
+          <t>474890</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>515183</t>
+          <t>517545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>837485</t>
+          <t>836555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>889216</t>
+          <t>889814</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,17%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>475979</t>
+          <t>477050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>554586</t>
+          <t>551520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>457239</t>
+          <t>459322</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>531074</t>
+          <t>533514</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951845</t>
+          <t>955675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1062309</t>
+          <t>1064105</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1142019</t>
+          <t>1145085</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1220626</t>
+          <t>1219555</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1177645</t>
+          <t>1175205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1251480</t>
+          <t>1249397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2343015</t>
+          <t>2341219</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2453479</t>
+          <t>2449649</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105268</t>
+          <t>107596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145355</t>
+          <t>146932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93524</t>
+          <t>94049</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130325</t>
+          <t>129195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213592</t>
+          <t>211112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>267601</t>
+          <t>264351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>353889</t>
+          <t>352312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>393976</t>
+          <t>391648</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>377995</t>
+          <t>379125</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>414796</t>
+          <t>414271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>739963</t>
+          <t>743213</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>793972</t>
+          <t>796452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>687976</t>
+          <t>687880</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>783656</t>
+          <t>781787</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>700814</t>
+          <t>702111</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>791991</t>
+          <t>795219</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1413411</t>
+          <t>1424152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1549998</t>
+          <t>1551894</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1869613</t>
+          <t>1871482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1965293</t>
+          <t>1965389</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2063922</t>
+          <t>2060694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2155099</t>
+          <t>2153802</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3959184</t>
+          <t>3957288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4095771</t>
+          <t>4085030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,15%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>71855</t>
+          <t>83653</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57664</t>
+          <t>65401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86944</t>
+          <t>102146</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>104901</t>
+          <t>114116</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91433</t>
+          <t>99253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121682</t>
+          <t>131553</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>176756</t>
+          <t>197769</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154606</t>
+          <t>175551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199094</t>
+          <t>223131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>411490</t>
+          <t>452427</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>396401</t>
+          <t>433934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425681</t>
+          <t>470679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>616715</t>
+          <t>670476</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>599934</t>
+          <t>653039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>630183</t>
+          <t>685339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1028205</t>
+          <t>1122903</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1005867</t>
+          <t>1097541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1050355</t>
+          <t>1145121</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>483345</t>
+          <t>536080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>483345</t>
+          <t>536080</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>483345</t>
+          <t>536080</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1204961</t>
+          <t>1320672</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1204961</t>
+          <t>1320672</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1204961</t>
+          <t>1320672</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>423516</t>
+          <t>452081</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>295770</t>
+          <t>408276</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>495897</t>
+          <t>499476</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>399063</t>
+          <t>407658</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>297009</t>
+          <t>374159</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>478431</t>
+          <t>446490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>822579</t>
+          <t>859738</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>670396</t>
+          <t>808770</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>945230</t>
+          <t>924217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1807021</t>
+          <t>1694397</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1734640</t>
+          <t>1647002</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1934767</t>
+          <t>1738202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1798200</t>
+          <t>1702266</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1718832</t>
+          <t>1663434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1900254</t>
+          <t>1735765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3605220</t>
+          <t>3396664</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3482569</t>
+          <t>3332185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3757403</t>
+          <t>3447632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>81,0%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2197263</t>
+          <t>2109924</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2197263</t>
+          <t>2109924</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2197263</t>
+          <t>2109924</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4427799</t>
+          <t>4256402</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4427799</t>
+          <t>4256402</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4427799</t>
+          <t>4256402</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>106157</t>
+          <t>112711</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86986</t>
+          <t>92471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128196</t>
+          <t>136019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>119566</t>
+          <t>141590</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104154</t>
+          <t>122617</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136708</t>
+          <t>161010</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>225723</t>
+          <t>254302</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200391</t>
+          <t>227043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253754</t>
+          <t>285152</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>525159</t>
+          <t>589130</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503120</t>
+          <t>565822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544330</t>
+          <t>609370</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>532045</t>
+          <t>582823</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514903</t>
+          <t>563403</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>547457</t>
+          <t>601796</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1057204</t>
+          <t>1171952</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1029173</t>
+          <t>1141102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1082536</t>
+          <t>1199211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>601529</t>
+          <t>648446</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>458468</t>
+          <t>595507</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>675248</t>
+          <t>702634</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>623530</t>
+          <t>663364</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>528827</t>
+          <t>621785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>714965</t>
+          <t>706839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1225059</t>
+          <t>1311809</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1062306</t>
+          <t>1246410</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1347249</t>
+          <t>1378326</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2743668</t>
+          <t>2735954</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2669949</t>
+          <t>2681766</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2886729</t>
+          <t>2788893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2946960</t>
+          <t>2955565</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2855525</t>
+          <t>2912090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3041663</t>
+          <t>2997144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5690628</t>
+          <t>5691520</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5568438</t>
+          <t>5625003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5853381</t>
+          <t>5756919</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3345197</t>
+          <t>3384400</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3345197</t>
+          <t>3384400</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3345197</t>
+          <t>3384400</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3570490</t>
+          <t>3618929</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3570490</t>
+          <t>3618929</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3570490</t>
+          <t>3618929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6915687</t>
+          <t>7003329</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6915687</t>
+          <t>7003329</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6915687</t>
+          <t>7003329</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
